--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/TENNESSEE_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/TENNESSEE_2016.xlsx
@@ -499,7 +499,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="9">
@@ -571,7 +571,7 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="13">
@@ -661,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="18">
@@ -679,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="D18">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="19">
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="D22">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="25">
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="31">
@@ -1111,7 +1111,7 @@
         <v>1</v>
       </c>
       <c r="D42">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="43">
@@ -1147,7 +1147,7 @@
         <v>10</v>
       </c>
       <c r="D44">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="45">
@@ -1291,7 +1291,7 @@
         <v>1</v>
       </c>
       <c r="D52">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="53">
@@ -1471,7 +1471,7 @@
         <v>1</v>
       </c>
       <c r="D62">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="63">
@@ -1525,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="D65">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="66">
@@ -1561,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="D67">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="68">
@@ -1633,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="D71">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="72">
@@ -1651,7 +1651,7 @@
         <v>1</v>
       </c>
       <c r="D72">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="73">
@@ -1831,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="D82">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="83">
@@ -1849,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="84">
@@ -1885,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="D85">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="86">
@@ -1993,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="D91">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="92">
@@ -2029,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="94">
@@ -2083,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="D96">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="97">
@@ -2101,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="D97">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="98">
@@ -2155,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="101">
@@ -2191,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="103">
@@ -2245,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="D105">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="106">
@@ -2281,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="108">
@@ -2317,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="D109">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="110">
@@ -2407,7 +2407,7 @@
         <v>1</v>
       </c>
       <c r="D114">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="115">
@@ -2479,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="D118">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="119">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C119">
         <v>1</v>
       </c>
       <c r="D119">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="120">
@@ -2551,7 +2551,7 @@
         <v>1</v>
       </c>
       <c r="D122">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="123">
@@ -2623,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="D126">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="127">
@@ -2713,7 +2713,7 @@
         <v>1</v>
       </c>
       <c r="D131">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="132">
@@ -2821,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="D137">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="138">
@@ -2839,7 +2839,7 @@
         <v>1</v>
       </c>
       <c r="D138">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="139">
@@ -2857,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="D139">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="140">
@@ -2875,7 +2875,7 @@
         <v>1</v>
       </c>
       <c r="D140">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="141">
@@ -3199,7 +3199,7 @@
         <v>10</v>
       </c>
       <c r="D158">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="159">
@@ -3307,7 +3307,7 @@
         <v>10</v>
       </c>
       <c r="D164">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="165">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C165">
@@ -3361,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="D167">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="168">
@@ -3415,7 +3415,7 @@
         <v>1</v>
       </c>
       <c r="D170">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="171">
@@ -3487,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="D174">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="175">
@@ -3505,7 +3505,7 @@
         <v>1</v>
       </c>
       <c r="D175">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="176">
@@ -3523,7 +3523,7 @@
         <v>1</v>
       </c>
       <c r="D176">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="177">
@@ -3577,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="D179">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="180">
@@ -3595,7 +3595,7 @@
         <v>1</v>
       </c>
       <c r="D180">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="181">
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="D181">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="182">
@@ -3631,7 +3631,7 @@
         <v>1</v>
       </c>
       <c r="D182">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="183">
@@ -3667,7 +3667,7 @@
         <v>1</v>
       </c>
       <c r="D184">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="185">
@@ -3721,7 +3721,7 @@
         <v>1</v>
       </c>
       <c r="D187">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="188">
@@ -3919,7 +3919,7 @@
         <v>10</v>
       </c>
       <c r="D198">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="199">
@@ -4027,7 +4027,7 @@
         <v>1</v>
       </c>
       <c r="D204">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="205">
@@ -4135,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="D210">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="211">
@@ -4333,7 +4333,7 @@
         <v>1</v>
       </c>
       <c r="D221">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="222">
@@ -4369,7 +4369,7 @@
         <v>1</v>
       </c>
       <c r="D223">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="224">
@@ -4387,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="D224">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="225">
@@ -4405,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="D225">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="226">
@@ -4423,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="D226">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="227">
@@ -4567,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="D234">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="235">
@@ -4603,7 +4603,7 @@
         <v>1</v>
       </c>
       <c r="D236">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="237">
@@ -4765,7 +4765,7 @@
         <v>1</v>
       </c>
       <c r="D245">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="246">
@@ -4801,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="D247">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="248">
@@ -4819,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="D248">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="249">
@@ -4855,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="D250">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="251">
@@ -4981,7 +4981,7 @@
         <v>1</v>
       </c>
       <c r="D257">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="258">
@@ -5035,7 +5035,7 @@
         <v>1</v>
       </c>
       <c r="D260">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="261">
@@ -5071,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="D262">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="263">
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="D267">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="268">
@@ -5179,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="D268">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="269">
@@ -5341,7 +5341,7 @@
         <v>10</v>
       </c>
       <c r="D277">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="278">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C280">
@@ -5791,7 +5791,7 @@
         <v>1</v>
       </c>
       <c r="D302">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="303">
@@ -5989,7 +5989,7 @@
         <v>1</v>
       </c>
       <c r="D313">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="314">
@@ -6187,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="D324">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="325">
@@ -6259,7 +6259,7 @@
         <v>1</v>
       </c>
       <c r="D328">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="329">
@@ -6457,7 +6457,7 @@
         <v>1</v>
       </c>
       <c r="D339">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="340">
@@ -6493,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="D341">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="342">
@@ -6547,7 +6547,7 @@
         <v>1</v>
       </c>
       <c r="D344">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="345">
@@ -6565,7 +6565,7 @@
         <v>1</v>
       </c>
       <c r="D345">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="346">
@@ -6637,7 +6637,7 @@
         <v>1</v>
       </c>
       <c r="D349">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="350">
@@ -6673,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="D351">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="352">
@@ -6961,7 +6961,7 @@
         <v>1</v>
       </c>
       <c r="D367">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="368">
@@ -7087,7 +7087,7 @@
         <v>1</v>
       </c>
       <c r="D374">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="375">
@@ -7213,7 +7213,7 @@
         <v>1</v>
       </c>
       <c r="D381">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="382">
@@ -7285,7 +7285,7 @@
         <v>1</v>
       </c>
       <c r="D385">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="386">
@@ -7465,7 +7465,7 @@
         <v>1</v>
       </c>
       <c r="D395">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="396">
@@ -7753,7 +7753,7 @@
         <v>1</v>
       </c>
       <c r="D411">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="412">
@@ -7825,7 +7825,7 @@
         <v>1</v>
       </c>
       <c r="D415">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="416">
@@ -7843,7 +7843,7 @@
         <v>1</v>
       </c>
       <c r="D416">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="417">
@@ -7879,7 +7879,7 @@
         <v>1</v>
       </c>
       <c r="D418">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="419">
@@ -7897,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="D419">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="420">
@@ -7915,7 +7915,7 @@
         <v>1</v>
       </c>
       <c r="D420">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="421">
@@ -8077,7 +8077,7 @@
         <v>1</v>
       </c>
       <c r="D429">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="430">
@@ -8131,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="D432">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="433">
@@ -8257,7 +8257,7 @@
         <v>1</v>
       </c>
       <c r="D439">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="440">
@@ -8347,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="D444">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="445">
@@ -8365,7 +8365,7 @@
         <v>1</v>
       </c>
       <c r="D445">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="446">
@@ -8491,7 +8491,7 @@
         <v>1</v>
       </c>
       <c r="D452">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="453">
@@ -8509,7 +8509,7 @@
         <v>1</v>
       </c>
       <c r="D453">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="454">
@@ -8527,7 +8527,7 @@
         <v>1</v>
       </c>
       <c r="D454">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="455">
@@ -8581,7 +8581,7 @@
         <v>1</v>
       </c>
       <c r="D457">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="458">
@@ -8635,7 +8635,7 @@
         <v>1</v>
       </c>
       <c r="D460">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="461">
@@ -8653,7 +8653,7 @@
         <v>1</v>
       </c>
       <c r="D461">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="462">
@@ -8689,7 +8689,7 @@
         <v>1</v>
       </c>
       <c r="D463">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="464">
@@ -8707,7 +8707,7 @@
         <v>1</v>
       </c>
       <c r="D464">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="465">
@@ -8725,7 +8725,7 @@
         <v>1</v>
       </c>
       <c r="D465">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="466">
@@ -8833,7 +8833,7 @@
         <v>1</v>
       </c>
       <c r="D471">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="472">
@@ -8959,7 +8959,7 @@
         <v>1</v>
       </c>
       <c r="D478">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="479">
@@ -9013,7 +9013,7 @@
         <v>1</v>
       </c>
       <c r="D481">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="482">
@@ -9049,7 +9049,7 @@
         <v>1</v>
       </c>
       <c r="D483">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="484">
@@ -9085,7 +9085,7 @@
         <v>1</v>
       </c>
       <c r="D485">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="486">
@@ -9103,7 +9103,7 @@
         <v>1</v>
       </c>
       <c r="D486">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="487">
@@ -9121,7 +9121,7 @@
         <v>1</v>
       </c>
       <c r="D487">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="488">
@@ -9157,7 +9157,7 @@
         <v>1</v>
       </c>
       <c r="D489">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="490">
@@ -9175,7 +9175,7 @@
         <v>1</v>
       </c>
       <c r="D490">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="491">
@@ -9301,7 +9301,7 @@
         <v>1</v>
       </c>
       <c r="D497">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="498">
@@ -9337,7 +9337,7 @@
         <v>1</v>
       </c>
       <c r="D499">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="500">
@@ -9391,7 +9391,7 @@
         <v>1</v>
       </c>
       <c r="D502">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="503">
@@ -9409,7 +9409,7 @@
         <v>1</v>
       </c>
       <c r="D503">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="504">
@@ -9463,7 +9463,7 @@
         <v>1</v>
       </c>
       <c r="D506">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="507">
@@ -9841,7 +9841,7 @@
         <v>1</v>
       </c>
       <c r="D527">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="528">
@@ -9859,7 +9859,7 @@
         <v>1</v>
       </c>
       <c r="D528">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="529">
@@ -9895,7 +9895,7 @@
         <v>1</v>
       </c>
       <c r="D530">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="531">
@@ -9931,7 +9931,7 @@
         <v>1</v>
       </c>
       <c r="D532">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="533">
@@ -10039,7 +10039,7 @@
         <v>102</v>
       </c>
       <c r="D538">
-        <v>0.009309117459158529</v>
+        <v>0.009309117459158528</v>
       </c>
     </row>
     <row r="539">
@@ -10057,7 +10057,7 @@
         <v>1</v>
       </c>
       <c r="D539">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="540">
@@ -10111,7 +10111,7 @@
         <v>1</v>
       </c>
       <c r="D542">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="543">
@@ -10129,7 +10129,7 @@
         <v>1</v>
       </c>
       <c r="D543">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="544">
@@ -10165,7 +10165,7 @@
         <v>1</v>
       </c>
       <c r="D545">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="546">
@@ -10219,7 +10219,7 @@
         <v>1</v>
       </c>
       <c r="D548">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="549">
@@ -10237,7 +10237,7 @@
         <v>1</v>
       </c>
       <c r="D549">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="550">
@@ -10435,7 +10435,7 @@
         <v>1</v>
       </c>
       <c r="D560">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="561">
@@ -10471,7 +10471,7 @@
         <v>1</v>
       </c>
       <c r="D562">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="563">
@@ -10543,7 +10543,7 @@
         <v>1</v>
       </c>
       <c r="D566">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="567">
@@ -10615,7 +10615,7 @@
         <v>1</v>
       </c>
       <c r="D570">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="571">
@@ -10705,7 +10705,7 @@
         <v>1</v>
       </c>
       <c r="D575">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="576">
@@ -10777,7 +10777,7 @@
         <v>1</v>
       </c>
       <c r="D579">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="580">
@@ -10813,7 +10813,7 @@
         <v>1</v>
       </c>
       <c r="D581">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="582">
@@ -10831,7 +10831,7 @@
         <v>1</v>
       </c>
       <c r="D582">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="583">
@@ -10885,7 +10885,7 @@
         <v>1</v>
       </c>
       <c r="D585">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="586">
@@ -10903,7 +10903,7 @@
         <v>1</v>
       </c>
       <c r="D586">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="587">
@@ -10957,7 +10957,7 @@
         <v>1</v>
       </c>
       <c r="D589">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="590">
@@ -11317,7 +11317,7 @@
         <v>1</v>
       </c>
       <c r="D609">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="610">
@@ -11335,7 +11335,7 @@
         <v>1</v>
       </c>
       <c r="D610">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="611">
@@ -11371,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="D612">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="613">
@@ -11389,7 +11389,7 @@
         <v>1</v>
       </c>
       <c r="D613">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="614">
@@ -11479,7 +11479,7 @@
         <v>1</v>
       </c>
       <c r="D618">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="619">
@@ -11497,7 +11497,7 @@
         <v>1</v>
       </c>
       <c r="D619">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="620">
@@ -11587,7 +11587,7 @@
         <v>1</v>
       </c>
       <c r="D624">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="625">
@@ -11695,7 +11695,7 @@
         <v>1</v>
       </c>
       <c r="D630">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="631">
@@ -11731,7 +11731,7 @@
         <v>1</v>
       </c>
       <c r="D632">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="633">
@@ -11749,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="D633">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="634">
@@ -12037,7 +12037,7 @@
         <v>1</v>
       </c>
       <c r="D649">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="650">
@@ -12091,7 +12091,7 @@
         <v>1</v>
       </c>
       <c r="D652">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="653">
@@ -12127,7 +12127,7 @@
         <v>1</v>
       </c>
       <c r="D654">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="655">
@@ -12145,7 +12145,7 @@
         <v>1</v>
       </c>
       <c r="D655">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="656">
@@ -12163,7 +12163,7 @@
         <v>1</v>
       </c>
       <c r="D656">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="657">
@@ -12199,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="D658">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="659">
@@ -12271,7 +12271,7 @@
         <v>1</v>
       </c>
       <c r="D662">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="663">
@@ -12325,7 +12325,7 @@
         <v>1</v>
       </c>
       <c r="D665">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="666">
@@ -12361,7 +12361,7 @@
         <v>1</v>
       </c>
       <c r="D667">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="668">
@@ -12379,7 +12379,7 @@
         <v>1</v>
       </c>
       <c r="D668">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="669">
@@ -12397,7 +12397,7 @@
         <v>10</v>
       </c>
       <c r="D669">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="670">
@@ -12433,7 +12433,7 @@
         <v>1</v>
       </c>
       <c r="D671">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="672">
@@ -12505,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="D675">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="676">
@@ -12559,7 +12559,7 @@
         <v>1</v>
       </c>
       <c r="D678">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="679">
@@ -12631,7 +12631,7 @@
         <v>1</v>
       </c>
       <c r="D682">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="683">
@@ -12649,7 +12649,7 @@
         <v>1</v>
       </c>
       <c r="D683">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="684">
@@ -12667,7 +12667,7 @@
         <v>1</v>
       </c>
       <c r="D684">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="685">
@@ -12757,7 +12757,7 @@
         <v>1</v>
       </c>
       <c r="D689">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="690">
@@ -12811,7 +12811,7 @@
         <v>1</v>
       </c>
       <c r="D692">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="693">
@@ -12847,7 +12847,7 @@
         <v>1</v>
       </c>
       <c r="D694">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="695">
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="D697">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="698">
@@ -12919,7 +12919,7 @@
         <v>1</v>
       </c>
       <c r="D698">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="699">
@@ -12973,7 +12973,7 @@
         <v>1</v>
       </c>
       <c r="D701">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="702">
@@ -13045,7 +13045,7 @@
         <v>1</v>
       </c>
       <c r="D705">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="706">
@@ -13063,7 +13063,7 @@
         <v>1</v>
       </c>
       <c r="D706">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="707">
@@ -13099,7 +13099,7 @@
         <v>1</v>
       </c>
       <c r="D708">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="709">
@@ -13135,7 +13135,7 @@
         <v>1</v>
       </c>
       <c r="D710">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="711">
@@ -13153,7 +13153,7 @@
         <v>1</v>
       </c>
       <c r="D711">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="712">
@@ -13171,7 +13171,7 @@
         <v>1</v>
       </c>
       <c r="D712">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="713">
@@ -13189,7 +13189,7 @@
         <v>1</v>
       </c>
       <c r="D713">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="714">
@@ -13207,7 +13207,7 @@
         <v>1</v>
       </c>
       <c r="D714">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="715">
@@ -13243,7 +13243,7 @@
         <v>1</v>
       </c>
       <c r="D716">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="717">
@@ -13261,7 +13261,7 @@
         <v>1</v>
       </c>
       <c r="D717">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="718">
@@ -13297,7 +13297,7 @@
         <v>1</v>
       </c>
       <c r="D719">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="720">
@@ -13315,7 +13315,7 @@
         <v>1</v>
       </c>
       <c r="D720">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="721">
@@ -13333,7 +13333,7 @@
         <v>1</v>
       </c>
       <c r="D721">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="722">
@@ -13351,7 +13351,7 @@
         <v>1</v>
       </c>
       <c r="D722">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="723">
@@ -13387,7 +13387,7 @@
         <v>1</v>
       </c>
       <c r="D724">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="725">
@@ -13405,7 +13405,7 @@
         <v>1</v>
       </c>
       <c r="D725">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="726">
@@ -13423,7 +13423,7 @@
         <v>1</v>
       </c>
       <c r="D726">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="727">
@@ -13441,7 +13441,7 @@
         <v>1</v>
       </c>
       <c r="D727">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="728">
@@ -13513,7 +13513,7 @@
         <v>1</v>
       </c>
       <c r="D731">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="732">
@@ -13549,7 +13549,7 @@
         <v>1</v>
       </c>
       <c r="D733">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="734">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C739">
@@ -13675,7 +13675,7 @@
         <v>1</v>
       </c>
       <c r="D740">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="741">
@@ -13747,7 +13747,7 @@
         <v>1</v>
       </c>
       <c r="D744">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="745">
@@ -13783,7 +13783,7 @@
         <v>1</v>
       </c>
       <c r="D746">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="747">
@@ -13819,7 +13819,7 @@
         <v>1</v>
       </c>
       <c r="D748">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="749">
@@ -13837,7 +13837,7 @@
         <v>1</v>
       </c>
       <c r="D749">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="750">
@@ -13855,7 +13855,7 @@
         <v>1</v>
       </c>
       <c r="D750">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="751">
@@ -13891,7 +13891,7 @@
         <v>1</v>
       </c>
       <c r="D752">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="753">
@@ -13927,7 +13927,7 @@
         <v>1</v>
       </c>
       <c r="D754">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="755">
@@ -13963,7 +13963,7 @@
         <v>1</v>
       </c>
       <c r="D756">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="757">
@@ -13999,7 +13999,7 @@
         <v>1</v>
       </c>
       <c r="D758">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="759">
@@ -14035,7 +14035,7 @@
         <v>1</v>
       </c>
       <c r="D760">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="761">
@@ -14053,7 +14053,7 @@
         <v>1</v>
       </c>
       <c r="D761">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="762">
@@ -14089,7 +14089,7 @@
         <v>1</v>
       </c>
       <c r="D763">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="764">
@@ -14107,7 +14107,7 @@
         <v>1</v>
       </c>
       <c r="D764">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="765">
@@ -14125,7 +14125,7 @@
         <v>10</v>
       </c>
       <c r="D765">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="766">
@@ -14143,7 +14143,7 @@
         <v>1</v>
       </c>
       <c r="D766">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="767">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C767">
@@ -14251,7 +14251,7 @@
         <v>1</v>
       </c>
       <c r="D772">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="773">
@@ -14305,7 +14305,7 @@
         <v>1</v>
       </c>
       <c r="D775">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="776">
@@ -14359,7 +14359,7 @@
         <v>1</v>
       </c>
       <c r="D778">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="779">
@@ -14395,7 +14395,7 @@
         <v>1</v>
       </c>
       <c r="D780">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="781">
@@ -14593,7 +14593,7 @@
         <v>1</v>
       </c>
       <c r="D791">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="792">
@@ -14629,7 +14629,7 @@
         <v>1</v>
       </c>
       <c r="D793">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="794">
@@ -14665,7 +14665,7 @@
         <v>1</v>
       </c>
       <c r="D795">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="796">
@@ -14683,7 +14683,7 @@
         <v>1</v>
       </c>
       <c r="D796">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="797">
@@ -14719,7 +14719,7 @@
         <v>1</v>
       </c>
       <c r="D798">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="799">
@@ -14737,7 +14737,7 @@
         <v>1</v>
       </c>
       <c r="D799">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="800">
@@ -14791,7 +14791,7 @@
         <v>1</v>
       </c>
       <c r="D802">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="803">
@@ -14827,7 +14827,7 @@
         <v>1</v>
       </c>
       <c r="D804">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="805">
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="D806">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="807">
@@ -14899,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="D808">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="809">
@@ -14917,7 +14917,7 @@
         <v>1</v>
       </c>
       <c r="D809">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="810">
@@ -14971,7 +14971,7 @@
         <v>1</v>
       </c>
       <c r="D812">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="813">
@@ -14989,7 +14989,7 @@
         <v>1</v>
       </c>
       <c r="D813">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="814">
@@ -15007,7 +15007,7 @@
         <v>1</v>
       </c>
       <c r="D814">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="815">
@@ -15025,7 +15025,7 @@
         <v>1</v>
       </c>
       <c r="D815">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="816">
@@ -15043,7 +15043,7 @@
         <v>1</v>
       </c>
       <c r="D816">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="817">
@@ -15169,7 +15169,7 @@
         <v>1</v>
       </c>
       <c r="D823">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="824">
@@ -15205,7 +15205,7 @@
         <v>1</v>
       </c>
       <c r="D825">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="826">
@@ -15223,7 +15223,7 @@
         <v>1</v>
       </c>
       <c r="D826">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="827">
@@ -15403,7 +15403,7 @@
         <v>1</v>
       </c>
       <c r="D836">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="837">
@@ -15432,14 +15432,14 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C838">
         <v>1</v>
       </c>
       <c r="D838">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="839">
@@ -15457,7 +15457,7 @@
         <v>1</v>
       </c>
       <c r="D839">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="840">
@@ -15547,7 +15547,7 @@
         <v>1</v>
       </c>
       <c r="D844">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="845">
@@ -15583,7 +15583,7 @@
         <v>1</v>
       </c>
       <c r="D846">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="847">
@@ -15601,7 +15601,7 @@
         <v>1</v>
       </c>
       <c r="D847">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="848">
@@ -15799,7 +15799,7 @@
         <v>1</v>
       </c>
       <c r="D858">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="859">
@@ -15853,7 +15853,7 @@
         <v>1</v>
       </c>
       <c r="D861">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="862">
@@ -15871,7 +15871,7 @@
         <v>1</v>
       </c>
       <c r="D862">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="863">
@@ -15889,7 +15889,7 @@
         <v>1</v>
       </c>
       <c r="D863">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="864">
@@ -15961,7 +15961,7 @@
         <v>1</v>
       </c>
       <c r="D867">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="868">
@@ -15979,7 +15979,7 @@
         <v>1</v>
       </c>
       <c r="D868">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="869">
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="D869">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="870">
@@ -16015,7 +16015,7 @@
         <v>1</v>
       </c>
       <c r="D870">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="871">
@@ -16069,7 +16069,7 @@
         <v>1</v>
       </c>
       <c r="D873">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="874">
@@ -16087,7 +16087,7 @@
         <v>1</v>
       </c>
       <c r="D874">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="875">
@@ -16123,7 +16123,7 @@
         <v>1</v>
       </c>
       <c r="D876">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="877">
@@ -16141,7 +16141,7 @@
         <v>1</v>
       </c>
       <c r="D877">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="878">
@@ -16159,7 +16159,7 @@
         <v>1</v>
       </c>
       <c r="D878">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="879">
@@ -16213,7 +16213,7 @@
         <v>1</v>
       </c>
       <c r="D881">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="882">
@@ -16303,7 +16303,7 @@
         <v>1</v>
       </c>
       <c r="D886">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="887">
@@ -16339,7 +16339,7 @@
         <v>1</v>
       </c>
       <c r="D888">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="889">
@@ -16393,7 +16393,7 @@
         <v>1</v>
       </c>
       <c r="D891">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="892">
@@ -16429,7 +16429,7 @@
         <v>1</v>
       </c>
       <c r="D893">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="894">
@@ -16447,7 +16447,7 @@
         <v>1</v>
       </c>
       <c r="D894">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="895">
@@ -16465,7 +16465,7 @@
         <v>1</v>
       </c>
       <c r="D895">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="896">
@@ -16483,7 +16483,7 @@
         <v>1</v>
       </c>
       <c r="D896">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="897">
@@ -16501,7 +16501,7 @@
         <v>1</v>
       </c>
       <c r="D897">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="898">
@@ -16609,7 +16609,7 @@
         <v>1</v>
       </c>
       <c r="D903">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="904">
@@ -16627,7 +16627,7 @@
         <v>1</v>
       </c>
       <c r="D904">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="905">
@@ -16645,7 +16645,7 @@
         <v>1</v>
       </c>
       <c r="D905">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="906">
@@ -16663,7 +16663,7 @@
         <v>1</v>
       </c>
       <c r="D906">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="907">
@@ -16699,7 +16699,7 @@
         <v>1</v>
       </c>
       <c r="D908">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="909">
@@ -16717,7 +16717,7 @@
         <v>1</v>
       </c>
       <c r="D909">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="910">
@@ -16735,7 +16735,7 @@
         <v>1</v>
       </c>
       <c r="D910">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="911">
@@ -16771,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="D912">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="913">
@@ -16807,7 +16807,7 @@
         <v>1</v>
       </c>
       <c r="D914">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="915">
@@ -16843,7 +16843,7 @@
         <v>1</v>
       </c>
       <c r="D916">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="917">
@@ -16933,7 +16933,7 @@
         <v>1</v>
       </c>
       <c r="D921">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="922">
@@ -16951,7 +16951,7 @@
         <v>1</v>
       </c>
       <c r="D922">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="923">
@@ -16987,7 +16987,7 @@
         <v>1</v>
       </c>
       <c r="D924">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="925">
@@ -17077,7 +17077,7 @@
         <v>1</v>
       </c>
       <c r="D929">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="930">
@@ -17149,7 +17149,7 @@
         <v>1</v>
       </c>
       <c r="D933">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="934">
@@ -17203,7 +17203,7 @@
         <v>1</v>
       </c>
       <c r="D936">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="937">
@@ -17221,7 +17221,7 @@
         <v>1</v>
       </c>
       <c r="D937">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="938">
@@ -17329,7 +17329,7 @@
         <v>1</v>
       </c>
       <c r="D943">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="944">
@@ -17347,7 +17347,7 @@
         <v>1</v>
       </c>
       <c r="D944">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="945">
@@ -17365,7 +17365,7 @@
         <v>1</v>
       </c>
       <c r="D945">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="946">
@@ -17491,7 +17491,7 @@
         <v>1</v>
       </c>
       <c r="D952">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="953">
@@ -17563,7 +17563,7 @@
         <v>1</v>
       </c>
       <c r="D956">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="957">
@@ -17581,7 +17581,7 @@
         <v>1</v>
       </c>
       <c r="D957">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="958">
@@ -17689,7 +17689,7 @@
         <v>1</v>
       </c>
       <c r="D963">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="964">
@@ -17761,7 +17761,7 @@
         <v>1</v>
       </c>
       <c r="D967">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="968">
@@ -17779,7 +17779,7 @@
         <v>10</v>
       </c>
       <c r="D968">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="969">
@@ -17959,7 +17959,7 @@
         <v>1</v>
       </c>
       <c r="D978">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="979">
@@ -18067,7 +18067,7 @@
         <v>1</v>
       </c>
       <c r="D984">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="985">
@@ -18175,7 +18175,7 @@
         <v>1</v>
       </c>
       <c r="D990">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="991">
@@ -18229,7 +18229,7 @@
         <v>1</v>
       </c>
       <c r="D993">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="994">
@@ -18247,7 +18247,7 @@
         <v>1</v>
       </c>
       <c r="D994">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="995">
@@ -18265,7 +18265,7 @@
         <v>10</v>
       </c>
       <c r="D995">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="996">
@@ -18301,7 +18301,7 @@
         <v>1</v>
       </c>
       <c r="D997">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="998">
@@ -18355,7 +18355,7 @@
         <v>1</v>
       </c>
       <c r="D1000">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1001">
@@ -18373,7 +18373,7 @@
         <v>10</v>
       </c>
       <c r="D1001">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="1002">
@@ -18553,7 +18553,7 @@
         <v>10</v>
       </c>
       <c r="D1011">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="1012">
@@ -18661,7 +18661,7 @@
         <v>1</v>
       </c>
       <c r="D1017">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1018">
@@ -18679,7 +18679,7 @@
         <v>1</v>
       </c>
       <c r="D1018">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1019">
@@ -18697,7 +18697,7 @@
         <v>1</v>
       </c>
       <c r="D1019">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1020">
@@ -18733,7 +18733,7 @@
         <v>1</v>
       </c>
       <c r="D1021">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1022">
@@ -18769,7 +18769,7 @@
         <v>1</v>
       </c>
       <c r="D1023">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1024">
@@ -18787,7 +18787,7 @@
         <v>1</v>
       </c>
       <c r="D1024">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1025">
@@ -18805,7 +18805,7 @@
         <v>1</v>
       </c>
       <c r="D1025">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1026">
@@ -18823,7 +18823,7 @@
         <v>1</v>
       </c>
       <c r="D1026">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1027">
@@ -18841,7 +18841,7 @@
         <v>1</v>
       </c>
       <c r="D1027">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1028">
@@ -18877,7 +18877,7 @@
         <v>1</v>
       </c>
       <c r="D1029">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1030">
@@ -18895,7 +18895,7 @@
         <v>1</v>
       </c>
       <c r="D1030">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1031">
@@ -18931,7 +18931,7 @@
         <v>1</v>
       </c>
       <c r="D1032">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1033">
@@ -18985,7 +18985,7 @@
         <v>1</v>
       </c>
       <c r="D1035">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1036">
@@ -19003,7 +19003,7 @@
         <v>1</v>
       </c>
       <c r="D1036">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1037">
@@ -19057,7 +19057,7 @@
         <v>1</v>
       </c>
       <c r="D1039">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1040">
@@ -19111,7 +19111,7 @@
         <v>1</v>
       </c>
       <c r="D1042">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1043">
@@ -19165,7 +19165,7 @@
         <v>1</v>
       </c>
       <c r="D1045">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1046">
@@ -19201,7 +19201,7 @@
         <v>1</v>
       </c>
       <c r="D1047">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1048">
@@ -19291,7 +19291,7 @@
         <v>1</v>
       </c>
       <c r="D1052">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1053">
@@ -19309,7 +19309,7 @@
         <v>1</v>
       </c>
       <c r="D1053">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1054">
@@ -19327,7 +19327,7 @@
         <v>1</v>
       </c>
       <c r="D1054">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1055">
@@ -19381,7 +19381,7 @@
         <v>1</v>
       </c>
       <c r="D1057">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1058">
@@ -19561,7 +19561,7 @@
         <v>1</v>
       </c>
       <c r="D1067">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1068">
@@ -19777,7 +19777,7 @@
         <v>1</v>
       </c>
       <c r="D1079">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1080">
@@ -19795,7 +19795,7 @@
         <v>1</v>
       </c>
       <c r="D1080">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1081">
@@ -19813,7 +19813,7 @@
         <v>1</v>
       </c>
       <c r="D1081">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1082">
@@ -19831,7 +19831,7 @@
         <v>1</v>
       </c>
       <c r="D1082">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1083">
@@ -19849,7 +19849,7 @@
         <v>1</v>
       </c>
       <c r="D1083">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1084">
@@ -19885,7 +19885,7 @@
         <v>1</v>
       </c>
       <c r="D1085">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1086">
@@ -19939,7 +19939,7 @@
         <v>1</v>
       </c>
       <c r="D1088">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1089">
@@ -19957,7 +19957,7 @@
         <v>1</v>
       </c>
       <c r="D1089">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1090">
@@ -20047,7 +20047,7 @@
         <v>1</v>
       </c>
       <c r="D1094">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1095">
@@ -20155,7 +20155,7 @@
         <v>10</v>
       </c>
       <c r="D1100">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="1101">
@@ -20173,7 +20173,7 @@
         <v>1</v>
       </c>
       <c r="D1101">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1102">
@@ -20209,7 +20209,7 @@
         <v>1</v>
       </c>
       <c r="D1103">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1104">
@@ -20245,7 +20245,7 @@
         <v>1</v>
       </c>
       <c r="D1105">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1106">
@@ -20263,7 +20263,7 @@
         <v>1</v>
       </c>
       <c r="D1106">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1107">
@@ -20317,7 +20317,7 @@
         <v>1</v>
       </c>
       <c r="D1109">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1110">
@@ -20335,7 +20335,7 @@
         <v>1</v>
       </c>
       <c r="D1110">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1111">
@@ -20389,7 +20389,7 @@
         <v>1</v>
       </c>
       <c r="D1113">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1114">
@@ -20425,7 +20425,7 @@
         <v>1</v>
       </c>
       <c r="D1115">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1116">
@@ -20443,7 +20443,7 @@
         <v>1</v>
       </c>
       <c r="D1116">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1117">
@@ -20479,7 +20479,7 @@
         <v>1</v>
       </c>
       <c r="D1118">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1119">
@@ -20497,7 +20497,7 @@
         <v>1</v>
       </c>
       <c r="D1119">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1120">
@@ -20533,7 +20533,7 @@
         <v>1</v>
       </c>
       <c r="D1121">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1122">
@@ -20551,7 +20551,7 @@
         <v>1</v>
       </c>
       <c r="D1122">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1123">
@@ -20587,7 +20587,7 @@
         <v>1</v>
       </c>
       <c r="D1124">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1125">
@@ -20605,7 +20605,7 @@
         <v>1</v>
       </c>
       <c r="D1125">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1126">
@@ -20623,7 +20623,7 @@
         <v>1</v>
       </c>
       <c r="D1126">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1127">
@@ -20677,7 +20677,7 @@
         <v>1</v>
       </c>
       <c r="D1129">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1130">
@@ -20695,7 +20695,7 @@
         <v>1</v>
       </c>
       <c r="D1130">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1131">
@@ -20911,7 +20911,7 @@
         <v>1</v>
       </c>
       <c r="D1142">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1143">
@@ -20947,7 +20947,7 @@
         <v>1</v>
       </c>
       <c r="D1144">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1145">
@@ -21073,7 +21073,7 @@
         <v>1</v>
       </c>
       <c r="D1151">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1152">
@@ -21325,7 +21325,7 @@
         <v>1</v>
       </c>
       <c r="D1165">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1166">
@@ -21361,7 +21361,7 @@
         <v>1</v>
       </c>
       <c r="D1167">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1168">
@@ -21397,7 +21397,7 @@
         <v>1</v>
       </c>
       <c r="D1169">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1170">
@@ -21415,7 +21415,7 @@
         <v>1</v>
       </c>
       <c r="D1170">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1171">
@@ -21559,7 +21559,7 @@
         <v>10</v>
       </c>
       <c r="D1178">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="1179">
@@ -21667,7 +21667,7 @@
         <v>1</v>
       </c>
       <c r="D1184">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1185">
@@ -21739,7 +21739,7 @@
         <v>1</v>
       </c>
       <c r="D1188">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1189">
@@ -21865,7 +21865,7 @@
         <v>10</v>
       </c>
       <c r="D1195">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="1196">
@@ -21901,7 +21901,7 @@
         <v>1</v>
       </c>
       <c r="D1197">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1198">
@@ -21937,7 +21937,7 @@
         <v>1</v>
       </c>
       <c r="D1199">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1200">
@@ -22045,7 +22045,7 @@
         <v>1</v>
       </c>
       <c r="D1205">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1206">
@@ -22081,7 +22081,7 @@
         <v>1</v>
       </c>
       <c r="D1207">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1208">
@@ -22099,7 +22099,7 @@
         <v>1</v>
       </c>
       <c r="D1208">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1209">
@@ -22135,7 +22135,7 @@
         <v>1</v>
       </c>
       <c r="D1210">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1211">
@@ -22225,7 +22225,7 @@
         <v>1</v>
       </c>
       <c r="D1215">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1216">
@@ -22243,7 +22243,7 @@
         <v>1</v>
       </c>
       <c r="D1216">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1217">
@@ -22315,7 +22315,7 @@
         <v>1</v>
       </c>
       <c r="D1220">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1221">
@@ -22351,7 +22351,7 @@
         <v>1</v>
       </c>
       <c r="D1222">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1223">
@@ -22459,7 +22459,7 @@
         <v>1</v>
       </c>
       <c r="D1228">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1229">
@@ -22513,7 +22513,7 @@
         <v>1</v>
       </c>
       <c r="D1231">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1232">
@@ -22585,7 +22585,7 @@
         <v>1</v>
       </c>
       <c r="D1235">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1236">
@@ -22657,7 +22657,7 @@
         <v>1</v>
       </c>
       <c r="D1239">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1240">
@@ -22693,7 +22693,7 @@
         <v>1</v>
       </c>
       <c r="D1241">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1242">
@@ -22801,7 +22801,7 @@
         <v>1</v>
       </c>
       <c r="D1247">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1248">
@@ -22855,7 +22855,7 @@
         <v>1</v>
       </c>
       <c r="D1250">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1251">
@@ -22891,7 +22891,7 @@
         <v>10</v>
       </c>
       <c r="D1252">
-        <v>0.0009126585744273067</v>
+        <v>0.0009126585744273068</v>
       </c>
     </row>
     <row r="1253">
@@ -22909,7 +22909,7 @@
         <v>1</v>
       </c>
       <c r="D1253">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1254">
@@ -22927,7 +22927,7 @@
         <v>1</v>
       </c>
       <c r="D1254">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1255">
@@ -22963,7 +22963,7 @@
         <v>1</v>
       </c>
       <c r="D1256">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1257">
@@ -22999,7 +22999,7 @@
         <v>1</v>
       </c>
       <c r="D1258">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1259">
@@ -23143,7 +23143,7 @@
         <v>1</v>
       </c>
       <c r="D1266">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1267">
@@ -23161,7 +23161,7 @@
         <v>1</v>
       </c>
       <c r="D1267">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1268">
@@ -23179,7 +23179,7 @@
         <v>1</v>
       </c>
       <c r="D1268">
-        <v>9.126585744273067E-05</v>
+        <v>9.126585744273068E-05</v>
       </c>
     </row>
     <row r="1269">
